--- a/library/rf.xlsx
+++ b/library/rf.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Git\elem_altium_db2\library\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitProjects\elem_altium_db2\library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{731DAF1D-7291-4010-BDDE-C9F4B4BCF6B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F837851-D6A1-41F1-B1D6-004CCB987A7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="795" yWindow="1905" windowWidth="21585" windowHeight="11775" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
   </bookViews>
   <sheets>
     <sheet name="rf" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="59">
   <si>
     <t>Part Number</t>
   </si>
@@ -193,6 +193,24 @@
   </si>
   <si>
     <t>Murata</t>
+  </si>
+  <si>
+    <t>MA8Serias</t>
+  </si>
+  <si>
+    <t>SFE10,7MS3G-A MA8Serias</t>
+  </si>
+  <si>
+    <t>SFE10,7MS3G-A_SMD</t>
+  </si>
+  <si>
+    <t>WR-SMP</t>
+  </si>
+  <si>
+    <t>WR-SMP SMP PCB SMT Plug</t>
+  </si>
+  <si>
+    <t>WURTH ELEKTRONIK</t>
   </si>
 </sst>
 </file>
@@ -571,7 +589,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67671D6E-5D55-4C0C-9FE7-A86F937C6875}">
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.85546875" customWidth="1"/>
@@ -579,7 +597,8 @@
     <col min="3" max="3" width="26.5703125" customWidth="1"/>
     <col min="4" max="4" width="22.42578125" customWidth="1"/>
     <col min="5" max="5" width="21" customWidth="1"/>
-    <col min="6" max="6" width="14.7109375" customWidth="1"/>
+    <col min="6" max="6" width="28.140625" customWidth="1"/>
+    <col min="7" max="7" width="21.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1000,6 +1019,52 @@
         <v>33</v>
       </c>
     </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>55</v>
+      </c>
+      <c r="B19" t="s">
+        <v>53</v>
+      </c>
+      <c r="C19" t="s">
+        <v>54</v>
+      </c>
+      <c r="D19" t="s">
+        <v>50</v>
+      </c>
+      <c r="E19" t="s">
+        <v>50</v>
+      </c>
+      <c r="F19" t="s">
+        <v>53</v>
+      </c>
+      <c r="G19" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>56</v>
+      </c>
+      <c r="B20" t="s">
+        <v>56</v>
+      </c>
+      <c r="C20" t="s">
+        <v>56</v>
+      </c>
+      <c r="D20" t="s">
+        <v>56</v>
+      </c>
+      <c r="E20" t="s">
+        <v>56</v>
+      </c>
+      <c r="F20" t="s">
+        <v>57</v>
+      </c>
+      <c r="G20" t="s">
+        <v>58</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/library/rf.xlsx
+++ b/library/rf.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitProjects\elem_altium_db2\library\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Git\elem_altium_db2\library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F837851-D6A1-41F1-B1D6-004CCB987A7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{433F44DC-E02F-41A2-91E8-3654692298D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
+    <workbookView xWindow="7935" yWindow="1935" windowWidth="21585" windowHeight="11775" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
   </bookViews>
   <sheets>
     <sheet name="rf" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="77">
   <si>
     <t>Part Number</t>
   </si>
@@ -211,6 +211,60 @@
   </si>
   <si>
     <t>WURTH ELEKTRONIK</t>
+  </si>
+  <si>
+    <t>HMC525ALC4</t>
+  </si>
+  <si>
+    <t>LCC-E-24-1</t>
+  </si>
+  <si>
+    <t>HMC525ALC4 LCC E-24-1</t>
+  </si>
+  <si>
+    <t>LCC E-24-1</t>
+  </si>
+  <si>
+    <t>3PEAK</t>
+  </si>
+  <si>
+    <t>SOT23-5</t>
+  </si>
+  <si>
+    <t>RS8901</t>
+  </si>
+  <si>
+    <t>TP1961-TR</t>
+  </si>
+  <si>
+    <t>TP1961-TR SOT23-5</t>
+  </si>
+  <si>
+    <t>Texas Instruments</t>
+  </si>
+  <si>
+    <t>THS4503</t>
+  </si>
+  <si>
+    <t>THS4503CDGNR</t>
+  </si>
+  <si>
+    <t>THS4503CDGNR 8-MSOP-EP</t>
+  </si>
+  <si>
+    <t>Skyworks Solutions</t>
+  </si>
+  <si>
+    <t>SKY16601-555LF</t>
+  </si>
+  <si>
+    <t>Mini Circuits</t>
+  </si>
+  <si>
+    <t>LFCN-6000D+</t>
+  </si>
+  <si>
+    <t>HFCN-5050+</t>
   </si>
 </sst>
 </file>
@@ -589,7 +643,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67671D6E-5D55-4C0C-9FE7-A86F937C6875}">
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.85546875" customWidth="1"/>
@@ -1065,6 +1119,144 @@
         <v>58</v>
       </c>
     </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>59</v>
+      </c>
+      <c r="B21" t="s">
+        <v>60</v>
+      </c>
+      <c r="C21" t="s">
+        <v>61</v>
+      </c>
+      <c r="D21" t="s">
+        <v>59</v>
+      </c>
+      <c r="E21" t="s">
+        <v>59</v>
+      </c>
+      <c r="F21" t="s">
+        <v>62</v>
+      </c>
+      <c r="G21" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>66</v>
+      </c>
+      <c r="B22" t="s">
+        <v>64</v>
+      </c>
+      <c r="C22" t="s">
+        <v>67</v>
+      </c>
+      <c r="D22" t="s">
+        <v>66</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="F22" t="s">
+        <v>64</v>
+      </c>
+      <c r="G22" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B23" t="s">
+        <v>23</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>76</v>
+      </c>
+      <c r="B24" t="s">
+        <v>76</v>
+      </c>
+      <c r="C24" t="s">
+        <v>76</v>
+      </c>
+      <c r="D24" t="s">
+        <v>76</v>
+      </c>
+      <c r="E24" t="s">
+        <v>76</v>
+      </c>
+      <c r="F24" t="s">
+        <v>76</v>
+      </c>
+      <c r="G24" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>75</v>
+      </c>
+      <c r="B25" t="s">
+        <v>75</v>
+      </c>
+      <c r="C25" t="s">
+        <v>75</v>
+      </c>
+      <c r="D25" t="s">
+        <v>75</v>
+      </c>
+      <c r="E25" t="s">
+        <v>75</v>
+      </c>
+      <c r="F25" t="s">
+        <v>75</v>
+      </c>
+      <c r="G25" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>73</v>
+      </c>
+      <c r="B26" t="s">
+        <v>73</v>
+      </c>
+      <c r="C26" t="s">
+        <v>73</v>
+      </c>
+      <c r="D26" t="s">
+        <v>73</v>
+      </c>
+      <c r="E26" t="s">
+        <v>73</v>
+      </c>
+      <c r="F26" t="s">
+        <v>73</v>
+      </c>
+      <c r="G26" t="s">
+        <v>72</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/library/rf.xlsx
+++ b/library/rf.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Git\elem_altium_db2\library\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitProjects\elem_altium_db2\library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{433F44DC-E02F-41A2-91E8-3654692298D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32328DD2-49A0-48B9-BFE9-2AD54423800F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7935" yWindow="1935" windowWidth="21585" windowHeight="11775" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
   </bookViews>
   <sheets>
     <sheet name="rf" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="80">
   <si>
     <t>Part Number</t>
   </si>
@@ -135,9 +135,6 @@
     <t>MTX2-73+ 12-QFN (3Х3)</t>
   </si>
   <si>
-    <t>Mimi-Circuits</t>
-  </si>
-  <si>
     <t>CD636</t>
   </si>
   <si>
@@ -265,6 +262,18 @@
   </si>
   <si>
     <t>HFCN-5050+</t>
+  </si>
+  <si>
+    <t>HMC431LP4E</t>
+  </si>
+  <si>
+    <t>24-QFN (4x4)</t>
+  </si>
+  <si>
+    <t>HMC431LP4E 24-QFN (4x4)</t>
+  </si>
+  <si>
+    <t>HMC407MS8G 8-MSOP-EP</t>
   </si>
 </sst>
 </file>
@@ -643,7 +652,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67671D6E-5D55-4C0C-9FE7-A86F937C6875}">
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.85546875" customWidth="1"/>
@@ -683,45 +692,46 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>15</v>
+        <v>76</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>15</v>
+        <v>77</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>15</v>
+        <v>78</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>15</v>
+        <v>76</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>15</v>
+        <v>76</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>15</v>
+        <v>77</v>
       </c>
       <c r="G2" t="s">
         <v>8</v>
       </c>
+      <c r="H2" s="2"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" t="s">
-        <v>12</v>
+      <c r="A3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>23</v>
       </c>
       <c r="G3" t="s">
         <v>8</v>
@@ -729,19 +739,19 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
         <v>10</v>
       </c>
       <c r="C4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D4" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E4" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
         <v>12</v>
@@ -751,20 +761,20 @@
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>16</v>
+      <c r="A5" t="s">
+        <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D5" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E5" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F5" t="s">
         <v>12</v>
@@ -774,23 +784,23 @@
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>19</v>
+      <c r="A6" s="2" t="s">
+        <v>16</v>
       </c>
       <c r="B6" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C6" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D6" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E6" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F6" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="G6" t="s">
         <v>8</v>
@@ -798,19 +808,19 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B7" t="s">
         <v>18</v>
       </c>
       <c r="C7" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D7" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E7" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F7" t="s">
         <v>18</v>
@@ -820,67 +830,67 @@
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>24</v>
+      <c r="A8" t="s">
+        <v>21</v>
       </c>
       <c r="B8" t="s">
-        <v>23</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>24</v>
+        <v>18</v>
+      </c>
+      <c r="C8" t="s">
+        <v>22</v>
+      </c>
+      <c r="D8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E8" t="s">
+        <v>21</v>
       </c>
       <c r="F8" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="G8" t="s">
         <v>8</v>
       </c>
-      <c r="I8" s="3"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>26</v>
+      <c r="A9" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="B9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C9" t="s">
-        <v>27</v>
-      </c>
-      <c r="D9" t="s">
-        <v>26</v>
-      </c>
-      <c r="E9" t="s">
-        <v>26</v>
+        <v>23</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="F9" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="G9" t="s">
         <v>8</v>
       </c>
+      <c r="I9" s="3"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B10" t="s">
         <v>12</v>
       </c>
       <c r="C10" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D10" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E10" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F10" t="s">
         <v>12</v>
@@ -891,324 +901,324 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B11" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="C11" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D11" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E11" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F11" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="G11" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B12" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C12" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D12" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="E12" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="F12" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="G12" t="s">
-        <v>33</v>
+        <v>73</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B13" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="C13" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D13" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="E13" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="F13" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="G13" t="s">
-        <v>40</v>
+        <v>73</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B14" t="s">
+        <v>36</v>
+      </c>
+      <c r="C14" t="s">
+        <v>38</v>
+      </c>
+      <c r="D14" t="s">
         <v>37</v>
       </c>
-      <c r="C14" t="s">
-        <v>42</v>
-      </c>
-      <c r="D14" t="s">
-        <v>41</v>
-      </c>
       <c r="E14" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F14" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G14" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="B15" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="C15" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="D15" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="E15" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="F15" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="G15" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="B16" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="C16" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="D16" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="E16" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="F16" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="G16" t="s">
-        <v>33</v>
+        <v>73</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="B17" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C17" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="D17" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="E17" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="F17" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G17" t="s">
-        <v>52</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B18" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C18" t="s">
+        <v>50</v>
+      </c>
+      <c r="D18" t="s">
         <v>49</v>
       </c>
-      <c r="D18" t="s">
-        <v>48</v>
-      </c>
       <c r="E18" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F18" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G18" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="B19" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="C19" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="D19" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E19" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="F19" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="G19" t="s">
-        <v>52</v>
+        <v>73</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B20" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C20" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D20" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="E20" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="F20" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="G20" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B21" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="C21" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D21" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="E21" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="F21" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="G21" t="s">
-        <v>8</v>
+        <v>57</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
+        <v>58</v>
+      </c>
+      <c r="B22" t="s">
+        <v>59</v>
+      </c>
+      <c r="C22" t="s">
+        <v>60</v>
+      </c>
+      <c r="D22" t="s">
+        <v>58</v>
+      </c>
+      <c r="E22" t="s">
+        <v>58</v>
+      </c>
+      <c r="F22" t="s">
+        <v>61</v>
+      </c>
+      <c r="G22" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>65</v>
+      </c>
+      <c r="B23" t="s">
+        <v>63</v>
+      </c>
+      <c r="C23" t="s">
         <v>66</v>
       </c>
-      <c r="B22" t="s">
+      <c r="D23" t="s">
+        <v>65</v>
+      </c>
+      <c r="E23" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="C22" t="s">
+      <c r="F23" t="s">
+        <v>63</v>
+      </c>
+      <c r="G23" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B24" t="s">
+        <v>23</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G24" s="2" t="s">
         <v>67</v>
-      </c>
-      <c r="D22" t="s">
-        <v>66</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="F22" t="s">
-        <v>64</v>
-      </c>
-      <c r="G22" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="B23" t="s">
-        <v>23</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>76</v>
-      </c>
-      <c r="B24" t="s">
-        <v>76</v>
-      </c>
-      <c r="C24" t="s">
-        <v>76</v>
-      </c>
-      <c r="D24" t="s">
-        <v>76</v>
-      </c>
-      <c r="E24" t="s">
-        <v>76</v>
-      </c>
-      <c r="F24" t="s">
-        <v>76</v>
-      </c>
-      <c r="G24" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -1231,30 +1241,53 @@
         <v>75</v>
       </c>
       <c r="G25" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
+        <v>74</v>
+      </c>
+      <c r="B26" t="s">
+        <v>74</v>
+      </c>
+      <c r="C26" t="s">
+        <v>74</v>
+      </c>
+      <c r="D26" t="s">
+        <v>74</v>
+      </c>
+      <c r="E26" t="s">
+        <v>74</v>
+      </c>
+      <c r="F26" t="s">
+        <v>74</v>
+      </c>
+      <c r="G26" t="s">
         <v>73</v>
       </c>
-      <c r="B26" t="s">
-        <v>73</v>
-      </c>
-      <c r="C26" t="s">
-        <v>73</v>
-      </c>
-      <c r="D26" t="s">
-        <v>73</v>
-      </c>
-      <c r="E26" t="s">
-        <v>73</v>
-      </c>
-      <c r="F26" t="s">
-        <v>73</v>
-      </c>
-      <c r="G26" t="s">
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
         <v>72</v>
+      </c>
+      <c r="B27" t="s">
+        <v>72</v>
+      </c>
+      <c r="C27" t="s">
+        <v>72</v>
+      </c>
+      <c r="D27" t="s">
+        <v>72</v>
+      </c>
+      <c r="E27" t="s">
+        <v>72</v>
+      </c>
+      <c r="F27" t="s">
+        <v>72</v>
+      </c>
+      <c r="G27" t="s">
+        <v>71</v>
       </c>
     </row>
   </sheetData>

--- a/library/rf.xlsx
+++ b/library/rf.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitProjects\elem_altium_db2\library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32328DD2-49A0-48B9-BFE9-2AD54423800F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C47D9A10-D6E9-4531-A064-572B840ECE2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="85">
   <si>
     <t>Part Number</t>
   </si>
@@ -274,6 +274,21 @@
   </si>
   <si>
     <t>HMC407MS8G 8-MSOP-EP</t>
+  </si>
+  <si>
+    <t>AVA-6123MP+</t>
+  </si>
+  <si>
+    <t>LHA-13LN+</t>
+  </si>
+  <si>
+    <t>Antenna PTFE 10.5 GHz</t>
+  </si>
+  <si>
+    <t>Antenna_10500MHz_PTFE</t>
+  </si>
+  <si>
+    <t>PMA3-5123+</t>
   </si>
 </sst>
 </file>
@@ -652,11 +667,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67671D6E-5D55-4C0C-9FE7-A86F937C6875}">
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21.85546875" customWidth="1"/>
-    <col min="2" max="2" width="13.140625" customWidth="1"/>
+    <col min="1" max="1" width="23.5703125" customWidth="1"/>
+    <col min="2" max="2" width="15.42578125" customWidth="1"/>
     <col min="3" max="3" width="26.5703125" customWidth="1"/>
     <col min="4" max="4" width="22.42578125" customWidth="1"/>
     <col min="5" max="5" width="21" customWidth="1"/>
@@ -1290,6 +1305,92 @@
         <v>71</v>
       </c>
     </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>80</v>
+      </c>
+      <c r="B28" t="s">
+        <v>77</v>
+      </c>
+      <c r="C28" t="s">
+        <v>80</v>
+      </c>
+      <c r="D28" t="s">
+        <v>80</v>
+      </c>
+      <c r="E28" t="s">
+        <v>80</v>
+      </c>
+      <c r="F28" t="s">
+        <v>77</v>
+      </c>
+      <c r="G28" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>81</v>
+      </c>
+      <c r="B29" t="s">
+        <v>30</v>
+      </c>
+      <c r="C29" t="s">
+        <v>81</v>
+      </c>
+      <c r="D29" t="s">
+        <v>81</v>
+      </c>
+      <c r="E29" t="s">
+        <v>81</v>
+      </c>
+      <c r="F29" t="s">
+        <v>30</v>
+      </c>
+      <c r="G29" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>83</v>
+      </c>
+      <c r="C30" t="s">
+        <v>83</v>
+      </c>
+      <c r="D30" t="s">
+        <v>83</v>
+      </c>
+      <c r="E30" t="s">
+        <v>83</v>
+      </c>
+      <c r="F30" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>84</v>
+      </c>
+      <c r="B31" t="s">
+        <v>12</v>
+      </c>
+      <c r="C31" t="s">
+        <v>84</v>
+      </c>
+      <c r="D31" t="s">
+        <v>84</v>
+      </c>
+      <c r="E31" t="s">
+        <v>84</v>
+      </c>
+      <c r="F31" t="s">
+        <v>12</v>
+      </c>
+      <c r="G31" t="s">
+        <v>73</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/library/rf.xlsx
+++ b/library/rf.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitProjects\elem_altium_db2\library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C47D9A10-D6E9-4531-A064-572B840ECE2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{239AD208-B881-4166-B52D-FF26221C1620}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="89">
   <si>
     <t>Part Number</t>
   </si>
@@ -289,13 +289,35 @@
   </si>
   <si>
     <t>PMA3-5123+</t>
+  </si>
+  <si>
+    <t>BGA9</t>
+  </si>
+  <si>
+    <t>Infenion</t>
+  </si>
+  <si>
+    <t>BGA9C1MN9</t>
+  </si>
+  <si>
+    <r>
+      <t>BGA9C1MN9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Inter"/>
+      </rPr>
+      <t>E6327XTSA1</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -318,6 +340,11 @@
       <family val="2"/>
       <charset val="204"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Inter"/>
     </font>
   </fonts>
   <fills count="3">
@@ -347,11 +374,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Accent 3 2" xfId="1" xr:uid="{07D6D35A-A25D-4183-ACA2-756DA14CBAEA}"/>
@@ -667,8 +695,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67671D6E-5D55-4C0C-9FE7-A86F937C6875}">
-  <dimension ref="A1:I31"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:I32"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.5703125" customWidth="1"/>
     <col min="2" max="2" width="15.42578125" customWidth="1"/>
@@ -679,7 +707,7 @@
     <col min="7" max="7" width="21.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -705,7 +733,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9">
       <c r="A2" s="2" t="s">
         <v>76</v>
       </c>
@@ -729,7 +757,7 @@
       </c>
       <c r="H2" s="2"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9">
       <c r="A3" s="2" t="s">
         <v>15</v>
       </c>
@@ -752,7 +780,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -775,7 +803,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -798,7 +826,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9">
       <c r="A6" s="2" t="s">
         <v>16</v>
       </c>
@@ -821,7 +849,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9">
       <c r="A7" t="s">
         <v>19</v>
       </c>
@@ -844,7 +872,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9">
       <c r="A8" t="s">
         <v>21</v>
       </c>
@@ -867,7 +895,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9">
       <c r="A9" s="2" t="s">
         <v>24</v>
       </c>
@@ -891,7 +919,7 @@
       </c>
       <c r="I9" s="3"/>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9">
       <c r="A10" t="s">
         <v>26</v>
       </c>
@@ -914,7 +942,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9">
       <c r="A11" t="s">
         <v>28</v>
       </c>
@@ -937,7 +965,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9">
       <c r="A12" t="s">
         <v>31</v>
       </c>
@@ -960,7 +988,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9">
       <c r="A13" t="s">
         <v>34</v>
       </c>
@@ -983,7 +1011,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9">
       <c r="A14" t="s">
         <v>37</v>
       </c>
@@ -1006,7 +1034,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9">
       <c r="A15" t="s">
         <v>40</v>
       </c>
@@ -1029,7 +1057,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9">
       <c r="A16" t="s">
         <v>31</v>
       </c>
@@ -1052,7 +1080,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7">
       <c r="A17" t="s">
         <v>43</v>
       </c>
@@ -1075,7 +1103,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7">
       <c r="A18" t="s">
         <v>49</v>
       </c>
@@ -1098,7 +1126,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7">
       <c r="A19" t="s">
         <v>47</v>
       </c>
@@ -1121,7 +1149,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7">
       <c r="A20" t="s">
         <v>54</v>
       </c>
@@ -1144,7 +1172,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7">
       <c r="A21" t="s">
         <v>55</v>
       </c>
@@ -1167,7 +1195,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7">
       <c r="A22" t="s">
         <v>58</v>
       </c>
@@ -1190,7 +1218,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7">
       <c r="A23" t="s">
         <v>65</v>
       </c>
@@ -1213,7 +1241,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7">
       <c r="A24" s="2" t="s">
         <v>69</v>
       </c>
@@ -1236,7 +1264,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7">
       <c r="A25" t="s">
         <v>75</v>
       </c>
@@ -1259,7 +1287,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7">
       <c r="A26" t="s">
         <v>74</v>
       </c>
@@ -1282,7 +1310,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7">
       <c r="A27" t="s">
         <v>72</v>
       </c>
@@ -1305,7 +1333,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7">
       <c r="A28" t="s">
         <v>80</v>
       </c>
@@ -1328,7 +1356,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7">
       <c r="A29" t="s">
         <v>81</v>
       </c>
@@ -1351,7 +1379,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7">
       <c r="A30" t="s">
         <v>83</v>
       </c>
@@ -1368,7 +1396,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7">
       <c r="A31" t="s">
         <v>84</v>
       </c>
@@ -1389,6 +1417,29 @@
       </c>
       <c r="G31" t="s">
         <v>73</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="E32" t="s">
+        <v>87</v>
+      </c>
+      <c r="F32" t="s">
+        <v>85</v>
+      </c>
+      <c r="G32" t="s">
+        <v>86</v>
       </c>
     </row>
   </sheetData>

--- a/library/rf.xlsx
+++ b/library/rf.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitProjects\elem_altium_db2\library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{239AD208-B881-4166-B52D-FF26221C1620}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB279B4A-B586-4207-BE14-ACF014C8CC6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="92">
   <si>
     <t>Part Number</t>
   </si>
@@ -311,6 +311,15 @@
       </rPr>
       <t>E6327XTSA1</t>
     </r>
+  </si>
+  <si>
+    <t>24-QFN (4x4) NO VIAS</t>
+  </si>
+  <si>
+    <t>32-QFN (5x5) NO VIAS</t>
+  </si>
+  <si>
+    <t>8-MSOP-EP NO VIAS</t>
   </si>
 </sst>
 </file>
@@ -374,12 +383,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Accent 3 2" xfId="1" xr:uid="{07D6D35A-A25D-4183-ACA2-756DA14CBAEA}"/>
@@ -749,8 +757,8 @@
       <c r="E2" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>77</v>
+      <c r="F2" t="s">
+        <v>89</v>
       </c>
       <c r="G2" t="s">
         <v>8</v>
@@ -773,8 +781,8 @@
       <c r="E3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="2" t="s">
-        <v>23</v>
+      <c r="F3" t="s">
+        <v>91</v>
       </c>
       <c r="G3" t="s">
         <v>8</v>
@@ -866,7 +874,7 @@
         <v>19</v>
       </c>
       <c r="F7" t="s">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="G7" t="s">
         <v>8</v>
@@ -889,7 +897,7 @@
         <v>21</v>
       </c>
       <c r="F8" t="s">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="G8" t="s">
         <v>8</v>
@@ -912,7 +920,7 @@
         <v>24</v>
       </c>
       <c r="F9" t="s">
-        <v>23</v>
+        <v>91</v>
       </c>
       <c r="G9" t="s">
         <v>8</v>
@@ -1350,7 +1358,7 @@
         <v>80</v>
       </c>
       <c r="F28" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="G28" t="s">
         <v>73</v>
@@ -1420,16 +1428,16 @@
       </c>
     </row>
     <row r="32" spans="1:7">
-      <c r="A32" s="4" t="s">
+      <c r="A32" t="s">
         <v>88</v>
       </c>
-      <c r="B32" s="4" t="s">
+      <c r="B32" t="s">
         <v>85</v>
       </c>
-      <c r="C32" s="4" t="s">
+      <c r="C32" t="s">
         <v>88</v>
       </c>
-      <c r="D32" s="4" t="s">
+      <c r="D32" t="s">
         <v>88</v>
       </c>
       <c r="E32" t="s">

--- a/library/rf.xlsx
+++ b/library/rf.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitProjects\elem_altium_db2\library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB279B4A-B586-4207-BE14-ACF014C8CC6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52C498D8-6744-4AB4-B8F5-8F86DC17C5FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="93">
   <si>
     <t>Part Number</t>
   </si>
@@ -320,6 +320,9 @@
   </si>
   <si>
     <t>8-MSOP-EP NO VIAS</t>
+  </si>
+  <si>
+    <t>SMP1330-085LF</t>
   </si>
 </sst>
 </file>
@@ -703,7 +706,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67671D6E-5D55-4C0C-9FE7-A86F937C6875}">
-  <dimension ref="A1:I32"/>
+  <dimension ref="A1:I33"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.5703125" customWidth="1"/>
@@ -1450,6 +1453,29 @@
         <v>86</v>
       </c>
     </row>
+    <row r="33" spans="1:7">
+      <c r="A33" t="s">
+        <v>92</v>
+      </c>
+      <c r="B33" t="s">
+        <v>92</v>
+      </c>
+      <c r="C33" t="s">
+        <v>92</v>
+      </c>
+      <c r="D33" t="s">
+        <v>92</v>
+      </c>
+      <c r="E33" t="s">
+        <v>92</v>
+      </c>
+      <c r="F33" t="s">
+        <v>92</v>
+      </c>
+      <c r="G33" t="s">
+        <v>71</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/library/rf.xlsx
+++ b/library/rf.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitProjects\elem_altium_db2\library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52C498D8-6744-4AB4-B8F5-8F86DC17C5FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F41FDF8-B062-48A4-A305-48D2C035C996}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="94">
   <si>
     <t>Part Number</t>
   </si>
@@ -323,6 +323,9 @@
   </si>
   <si>
     <t>SMP1330-085LF</t>
+  </si>
+  <si>
+    <t>SKY16603-632LF</t>
   </si>
 </sst>
 </file>
@@ -706,7 +709,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67671D6E-5D55-4C0C-9FE7-A86F937C6875}">
-  <dimension ref="A1:I33"/>
+  <dimension ref="A1:I34"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.5703125" customWidth="1"/>
@@ -1476,6 +1479,29 @@
         <v>71</v>
       </c>
     </row>
+    <row r="34" spans="1:7">
+      <c r="A34" t="s">
+        <v>93</v>
+      </c>
+      <c r="B34" t="s">
+        <v>93</v>
+      </c>
+      <c r="C34" t="s">
+        <v>93</v>
+      </c>
+      <c r="D34" t="s">
+        <v>93</v>
+      </c>
+      <c r="E34" t="s">
+        <v>93</v>
+      </c>
+      <c r="F34" t="s">
+        <v>93</v>
+      </c>
+      <c r="G34" t="s">
+        <v>71</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/library/rf.xlsx
+++ b/library/rf.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitProjects\elem_altium_db2\library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F41FDF8-B062-48A4-A305-48D2C035C996}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C2AEFBE-3D2B-421B-B7A8-5108873C2CDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="99">
   <si>
     <t>Part Number</t>
   </si>
@@ -326,6 +326,41 @@
   </si>
   <si>
     <t>SKY16603-632LF</t>
+  </si>
+  <si>
+    <t>24-QFN (5x5)</t>
+  </si>
+  <si>
+    <r>
+      <t>QPA1019</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Inter"/>
+      </rPr>
+      <t>TR7</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>QPA1019</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Inter"/>
+      </rPr>
+      <t>TR7 24-QFN (5x5)</t>
+    </r>
+  </si>
+  <si>
+    <t>QPA1019</t>
+  </si>
+  <si>
+    <t>QORVO</t>
   </si>
 </sst>
 </file>
@@ -709,7 +744,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67671D6E-5D55-4C0C-9FE7-A86F937C6875}">
-  <dimension ref="A1:I34"/>
+  <dimension ref="A1:I35"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.5703125" customWidth="1"/>
@@ -1502,6 +1537,29 @@
         <v>71</v>
       </c>
     </row>
+    <row r="35" spans="1:7">
+      <c r="A35" t="s">
+        <v>95</v>
+      </c>
+      <c r="B35" t="s">
+        <v>94</v>
+      </c>
+      <c r="C35" t="s">
+        <v>96</v>
+      </c>
+      <c r="D35" t="s">
+        <v>95</v>
+      </c>
+      <c r="E35" t="s">
+        <v>97</v>
+      </c>
+      <c r="F35" t="s">
+        <v>94</v>
+      </c>
+      <c r="G35" t="s">
+        <v>98</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/library/rf.xlsx
+++ b/library/rf.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10112"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitProjects\elem_altium_db2\library\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/garou/Documents/work/elem_altium_db2/library/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C2AEFBE-3D2B-421B-B7A8-5108873C2CDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{378664B6-D4E6-AF4A-AED2-013B166A7FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
   </bookViews>
   <sheets>
     <sheet name="rf" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="108">
   <si>
     <t>Part Number</t>
   </si>
@@ -87,54 +87,30 @@
     <t>HMC717ALP3E</t>
   </si>
   <si>
-    <t>HMC717ALP3E 16-QFN (3X3)</t>
-  </si>
-  <si>
-    <t>32-QFN (5x5)</t>
-  </si>
-  <si>
     <t>ADF4355-3BCPZ</t>
   </si>
   <si>
-    <t>ADF4355-3BCPZ 32-QFN (5x5)</t>
-  </si>
-  <si>
     <t>ADF5356</t>
   </si>
   <si>
-    <t>ADF5356 32-QFN (5x5)</t>
-  </si>
-  <si>
     <t>8-MSOP-EP</t>
   </si>
   <si>
     <t>HMC220B</t>
   </si>
   <si>
-    <t>HMC220B 8-MSOP-EP</t>
-  </si>
-  <si>
     <t>HMC369LP3</t>
   </si>
   <si>
-    <t>HMC369LP3 16-QFN (3X3)</t>
-  </si>
-  <si>
     <t>HMC451LP3</t>
   </si>
   <si>
-    <t>HMC451LP3 16-QFN (3X3)</t>
-  </si>
-  <si>
     <t>12-QFN (3Х3)</t>
   </si>
   <si>
     <t>MTX2-73+</t>
   </si>
   <si>
-    <t>MTX2-73+ 12-QFN (3Х3)</t>
-  </si>
-  <si>
     <t>CD636</t>
   </si>
   <si>
@@ -150,18 +126,12 @@
     <t>MAAM-011206</t>
   </si>
   <si>
-    <t>MAAM-011206 6-TDFN</t>
-  </si>
-  <si>
     <t>MACOM</t>
   </si>
   <si>
     <t>MADL-011023-14150T</t>
   </si>
   <si>
-    <t>MADL-011023-14150T 6-TDFN</t>
-  </si>
-  <si>
     <t>PL-264</t>
   </si>
   <si>
@@ -246,9 +216,6 @@
     <t>THS4503CDGNR</t>
   </si>
   <si>
-    <t>THS4503CDGNR 8-MSOP-EP</t>
-  </si>
-  <si>
     <t>Skyworks Solutions</t>
   </si>
   <si>
@@ -265,15 +232,6 @@
   </si>
   <si>
     <t>HMC431LP4E</t>
-  </si>
-  <si>
-    <t>24-QFN (4x4)</t>
-  </si>
-  <si>
-    <t>HMC431LP4E 24-QFN (4x4)</t>
-  </si>
-  <si>
-    <t>HMC407MS8G 8-MSOP-EP</t>
   </si>
   <si>
     <t>AVA-6123MP+</t>
@@ -344,6 +302,102 @@
     </r>
   </si>
   <si>
+    <t>QPA1019</t>
+  </si>
+  <si>
+    <t>QORVO</t>
+  </si>
+  <si>
+    <t>HMC431LP4E QFN-24 (4x4)</t>
+  </si>
+  <si>
+    <t>QFN-24 (4x4)</t>
+  </si>
+  <si>
+    <t>MSOP-8</t>
+  </si>
+  <si>
+    <t>HMC407MS8G MSOP-8</t>
+  </si>
+  <si>
+    <t>QFN-16 (3X3)</t>
+  </si>
+  <si>
+    <t>HMC717ALP3E QFN-16 (3X3)</t>
+  </si>
+  <si>
+    <t>QFN-32 (5x5)</t>
+  </si>
+  <si>
+    <t>ADF4355-3BCPZ QFN-32 (5x5)</t>
+  </si>
+  <si>
+    <t>ADF5356 QFN-32 (5x5)</t>
+  </si>
+  <si>
+    <t>HMC220B MSOP-8</t>
+  </si>
+  <si>
+    <t>HMC369LP3 QFN-16 (3X3)</t>
+  </si>
+  <si>
+    <t>HMC451LP3 QFN-16 (3X3)</t>
+  </si>
+  <si>
+    <t>MTX2-73+ QFN-12 (3Х3)</t>
+  </si>
+  <si>
+    <t>QFN-12 (3Х3)</t>
+  </si>
+  <si>
+    <t>TDFN-6</t>
+  </si>
+  <si>
+    <t>MAAM-011206 TDFN-6</t>
+  </si>
+  <si>
+    <t>MADL-011023-14150T TDFN-6</t>
+  </si>
+  <si>
+    <t>THS4503CDGNR MSOP-8</t>
+  </si>
+  <si>
+    <t>AVA-6123MP+ QFN-24 (4x4)</t>
+  </si>
+  <si>
+    <t>LHA-13LN+ QFN-12 (3Х3)</t>
+  </si>
+  <si>
+    <t>PMA3-5123+ QFN-16 (3X3)</t>
+  </si>
+  <si>
+    <r>
+      <t>BGA9C1MN9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Inter"/>
+      </rPr>
+      <t>E6327XTSA1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> BGA9</t>
+    </r>
+  </si>
+  <si>
+    <t>QFN-24 (5x5)</t>
+  </si>
+  <si>
     <r>
       <t>QPA1019</t>
     </r>
@@ -353,14 +407,8 @@
         <color rgb="FF000000"/>
         <rFont val="Inter"/>
       </rPr>
-      <t>TR7 24-QFN (5x5)</t>
+      <t>TR7 QFN-24 (5x5)</t>
     </r>
-  </si>
-  <si>
-    <t>QPA1019</t>
-  </si>
-  <si>
-    <t>QORVO</t>
   </si>
 </sst>
 </file>
@@ -431,8 +479,8 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
     <cellStyle name="Accent 3 2" xfId="1" xr:uid="{07D6D35A-A25D-4183-ACA2-756DA14CBAEA}"/>
-    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -448,9 +496,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office 2013–2022">
   <a:themeElements>
-    <a:clrScheme name="Стандартная">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -488,7 +536,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Стандартная">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -594,7 +642,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Стандартная">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -736,7 +784,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -745,15 +793,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67671D6E-5D55-4C0C-9FE7-A86F937C6875}">
   <dimension ref="A1:I35"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="23.5703125" customWidth="1"/>
-    <col min="2" max="2" width="15.42578125" customWidth="1"/>
-    <col min="3" max="3" width="26.5703125" customWidth="1"/>
-    <col min="4" max="4" width="22.42578125" customWidth="1"/>
-    <col min="5" max="5" width="21" customWidth="1"/>
-    <col min="6" max="6" width="28.140625" customWidth="1"/>
-    <col min="7" max="7" width="21.140625" customWidth="1"/>
+    <col min="1" max="2" width="20.83203125" customWidth="1"/>
+    <col min="3" max="3" width="25.83203125" customWidth="1"/>
+    <col min="4" max="8" width="20.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -784,22 +828,22 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="2" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="F2" t="s">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="G2" t="s">
         <v>8</v>
@@ -811,10 +855,10 @@
         <v>15</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>23</v>
+        <v>86</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>15</v>
@@ -823,7 +867,7 @@
         <v>15</v>
       </c>
       <c r="F3" t="s">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="G3" t="s">
         <v>8</v>
@@ -880,10 +924,10 @@
         <v>16</v>
       </c>
       <c r="B6" t="s">
-        <v>12</v>
+        <v>88</v>
       </c>
       <c r="C6" t="s">
-        <v>17</v>
+        <v>89</v>
       </c>
       <c r="D6" t="s">
         <v>16</v>
@@ -900,22 +944,22 @@
     </row>
     <row r="7" spans="1:9">
       <c r="A7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B7" t="s">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="C7" t="s">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="D7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F7" t="s">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="G7" t="s">
         <v>8</v>
@@ -923,22 +967,22 @@
     </row>
     <row r="8" spans="1:9">
       <c r="A8" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B8" t="s">
+        <v>90</v>
+      </c>
+      <c r="C8" t="s">
+        <v>92</v>
+      </c>
+      <c r="D8" t="s">
         <v>18</v>
       </c>
-      <c r="C8" t="s">
-        <v>22</v>
-      </c>
-      <c r="D8" t="s">
-        <v>21</v>
-      </c>
       <c r="E8" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F8" t="s">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="G8" t="s">
         <v>8</v>
@@ -946,22 +990,22 @@
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B9" t="s">
-        <v>23</v>
+        <v>86</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>25</v>
+        <v>93</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F9" t="s">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="G9" t="s">
         <v>8</v>
@@ -970,19 +1014,19 @@
     </row>
     <row r="10" spans="1:9">
       <c r="A10" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="B10" t="s">
-        <v>12</v>
+        <v>88</v>
       </c>
       <c r="C10" t="s">
-        <v>27</v>
+        <v>94</v>
       </c>
       <c r="D10" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="E10" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F10" t="s">
         <v>12</v>
@@ -993,19 +1037,19 @@
     </row>
     <row r="11" spans="1:9">
       <c r="A11" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="B11" t="s">
-        <v>12</v>
+        <v>88</v>
       </c>
       <c r="C11" t="s">
-        <v>29</v>
+        <v>95</v>
       </c>
       <c r="D11" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="E11" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="F11" t="s">
         <v>12</v>
@@ -1016,252 +1060,252 @@
     </row>
     <row r="12" spans="1:9">
       <c r="A12" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="B12" t="s">
-        <v>30</v>
+        <v>97</v>
       </c>
       <c r="C12" t="s">
-        <v>32</v>
+        <v>96</v>
       </c>
       <c r="D12" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="E12" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="F12" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="G12" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="B13" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="C13" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="D13" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="E13" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="F13" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="G13" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="B14" t="s">
-        <v>36</v>
+        <v>98</v>
       </c>
       <c r="C14" t="s">
-        <v>38</v>
+        <v>99</v>
       </c>
       <c r="D14" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="E14" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="F14" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="G14" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="B15" t="s">
-        <v>36</v>
+        <v>98</v>
       </c>
       <c r="C15" t="s">
-        <v>41</v>
+        <v>100</v>
       </c>
       <c r="D15" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="E15" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="F15" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="G15" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="B16" t="s">
-        <v>30</v>
+        <v>97</v>
       </c>
       <c r="C16" t="s">
-        <v>32</v>
+        <v>96</v>
       </c>
       <c r="D16" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="E16" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="F16" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="G16" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="B17" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="C17" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="D17" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="E17" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="F17" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G17" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="B18" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="C18" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="D18" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="E18" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="F18" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="G18" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="B19" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="C19" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="D19" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="E19" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="F19" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="G19" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="B20" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="C20" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="D20" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="E20" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="F20" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="G20" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="B21" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="C21" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="D21" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="E21" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="F21" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="G21" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="B22" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="C22" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="D22" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="E22" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="F22" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="G22" t="s">
         <v>8</v>
@@ -1269,295 +1313,280 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="B23" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="C23" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="D23" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="F23" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="G23" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24" s="2" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="B24" t="s">
-        <v>23</v>
+        <v>86</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>70</v>
+        <v>101</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25" t="s">
-        <v>75</v>
-      </c>
-      <c r="B25" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="C25" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="D25" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="E25" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="F25" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="G25" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
     </row>
     <row r="26" spans="1:7">
       <c r="A26" t="s">
-        <v>74</v>
-      </c>
-      <c r="B26" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="C26" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="D26" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="E26" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="F26" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="G26" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
     </row>
     <row r="27" spans="1:7">
       <c r="A27" t="s">
-        <v>72</v>
-      </c>
-      <c r="B27" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="C27" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="D27" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="E27" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="F27" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="G27" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
     </row>
     <row r="28" spans="1:7">
       <c r="A28" t="s">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="B28" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="C28" t="s">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="D28" t="s">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="E28" t="s">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="F28" t="s">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="G28" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
     </row>
     <row r="29" spans="1:7">
       <c r="A29" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="B29" t="s">
-        <v>30</v>
+        <v>97</v>
       </c>
       <c r="C29" t="s">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="D29" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="E29" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="F29" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="G29" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
     </row>
     <row r="30" spans="1:7">
       <c r="A30" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="C30" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="D30" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="E30" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="F30" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
     </row>
     <row r="31" spans="1:7">
       <c r="A31" t="s">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="B31" t="s">
-        <v>12</v>
+        <v>88</v>
       </c>
       <c r="C31" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="D31" t="s">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="E31" t="s">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="F31" t="s">
         <v>12</v>
       </c>
       <c r="G31" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
     </row>
     <row r="32" spans="1:7">
       <c r="A32" t="s">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="B32" t="s">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="C32" t="s">
-        <v>88</v>
+        <v>105</v>
       </c>
       <c r="D32" t="s">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="E32" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="F32" t="s">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="G32" t="s">
-        <v>86</v>
+        <v>72</v>
       </c>
     </row>
     <row r="33" spans="1:7">
       <c r="A33" t="s">
-        <v>92</v>
-      </c>
-      <c r="B33" t="s">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="C33" t="s">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="D33" t="s">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="E33" t="s">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="F33" t="s">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="G33" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
     </row>
     <row r="34" spans="1:7">
       <c r="A34" t="s">
-        <v>93</v>
-      </c>
-      <c r="B34" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="C34" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="D34" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="E34" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="F34" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="G34" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
     </row>
     <row r="35" spans="1:7">
       <c r="A35" t="s">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="B35" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="C35" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="D35" t="s">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="E35" t="s">
-        <v>97</v>
+        <v>82</v>
       </c>
       <c r="F35" t="s">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="G35" t="s">
-        <v>98</v>
+        <v>83</v>
       </c>
     </row>
   </sheetData>

--- a/library/rf.xlsx
+++ b/library/rf.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10112"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/garou/Documents/work/elem_altium_db2/library/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitProjects\elem_altium_db2\library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{378664B6-D4E6-AF4A-AED2-013B166A7FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9216F90-BBE8-4932-ADCF-8BBC8EA14D2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
   </bookViews>
   <sheets>
     <sheet name="rf" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="110">
   <si>
     <t>Part Number</t>
   </si>
@@ -409,6 +409,12 @@
       </rPr>
       <t>TR7 QFN-24 (5x5)</t>
     </r>
+  </si>
+  <si>
+    <t>DEA165550BT-2230C2-H</t>
+  </si>
+  <si>
+    <t>TDK</t>
   </si>
 </sst>
 </file>
@@ -479,8 +485,8 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
+    <cellStyle name="Accent 3 2" xfId="1" xr:uid="{07D6D35A-A25D-4183-ACA2-756DA14CBAEA}"/>
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
-    <cellStyle name="Accent 3 2" xfId="1" xr:uid="{07D6D35A-A25D-4183-ACA2-756DA14CBAEA}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -496,9 +502,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office 2013–2022">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Стандартная">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -536,7 +542,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Стандартная">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -642,7 +648,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Стандартная">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -784,7 +790,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -792,12 +798,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67671D6E-5D55-4C0C-9FE7-A86F937C6875}">
-  <dimension ref="A1:I35"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <dimension ref="A1:I36"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="25.83203125" customWidth="1"/>
-    <col min="4" max="8" width="20.83203125" customWidth="1"/>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="20.85546875" customWidth="1"/>
+    <col min="3" max="3" width="28.7109375" customWidth="1"/>
+    <col min="4" max="4" width="25.28515625" customWidth="1"/>
+    <col min="5" max="5" width="24.140625" customWidth="1"/>
+    <col min="6" max="6" width="23.42578125" customWidth="1"/>
+    <col min="7" max="8" width="20.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -1589,6 +1599,26 @@
         <v>83</v>
       </c>
     </row>
+    <row r="36" spans="1:7">
+      <c r="A36" t="s">
+        <v>108</v>
+      </c>
+      <c r="C36" t="s">
+        <v>108</v>
+      </c>
+      <c r="D36" t="s">
+        <v>108</v>
+      </c>
+      <c r="E36" t="s">
+        <v>78</v>
+      </c>
+      <c r="F36" t="s">
+        <v>108</v>
+      </c>
+      <c r="G36" t="s">
+        <v>109</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/library/rf.xlsx
+++ b/library/rf.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitProjects\elem_altium_db2\library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9216F90-BBE8-4932-ADCF-8BBC8EA14D2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{317B86A5-723F-401D-A63D-F19E4ABEA2B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
   </bookViews>
   <sheets>
     <sheet name="rf" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="112">
   <si>
     <t>Part Number</t>
   </si>
@@ -415,6 +415,12 @@
   </si>
   <si>
     <t>TDK</t>
+  </si>
+  <si>
+    <t>HMC624ALP4E</t>
+  </si>
+  <si>
+    <t>24-QFN (4x4)</t>
   </si>
 </sst>
 </file>
@@ -798,7 +804,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67671D6E-5D55-4C0C-9FE7-A86F937C6875}">
-  <dimension ref="A1:I36"/>
+  <dimension ref="A1:I37"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -1619,6 +1625,29 @@
         <v>109</v>
       </c>
     </row>
+    <row r="37" spans="1:7">
+      <c r="A37" t="s">
+        <v>110</v>
+      </c>
+      <c r="B37" t="s">
+        <v>85</v>
+      </c>
+      <c r="C37" t="s">
+        <v>110</v>
+      </c>
+      <c r="D37" t="s">
+        <v>110</v>
+      </c>
+      <c r="E37" t="s">
+        <v>110</v>
+      </c>
+      <c r="F37" t="s">
+        <v>111</v>
+      </c>
+      <c r="G37" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/library/rf.xlsx
+++ b/library/rf.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitProjects\elem_altium_db2\library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{317B86A5-723F-401D-A63D-F19E4ABEA2B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CEDB073-A182-41B1-83FC-053D76B2746C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="114">
   <si>
     <t>Part Number</t>
   </si>
@@ -421,6 +421,12 @@
   </si>
   <si>
     <t>24-QFN (4x4)</t>
+  </si>
+  <si>
+    <t>5300CF15A0950</t>
+  </si>
+  <si>
+    <t>EIS</t>
   </si>
 </sst>
 </file>
@@ -804,7 +810,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67671D6E-5D55-4C0C-9FE7-A86F937C6875}">
-  <dimension ref="A1:I37"/>
+  <dimension ref="A1:I38"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -1648,6 +1654,26 @@
         <v>8</v>
       </c>
     </row>
+    <row r="38" spans="1:7">
+      <c r="A38" t="s">
+        <v>112</v>
+      </c>
+      <c r="C38" t="s">
+        <v>112</v>
+      </c>
+      <c r="D38" t="s">
+        <v>112</v>
+      </c>
+      <c r="E38" t="s">
+        <v>112</v>
+      </c>
+      <c r="F38" t="s">
+        <v>112</v>
+      </c>
+      <c r="G38" t="s">
+        <v>113</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
